--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/maule.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5516,7 +5516,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2440-469-CM26</t>
+          <t>2827-353-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5536,17 +5536,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>5386.23</v>
+        <v>24676.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2827-353-CM26</t>
+          <t>2440-469-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5597,17 +5597,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>24676.6</v>
+        <v>5386.23</v>
       </c>
     </row>
     <row r="86">
@@ -7773,7 +7773,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2827-415-CM26</t>
+          <t>1233619-742-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1070.98</v>
+        <v>2287.83</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1233619-742-CM26</t>
+          <t>2827-415-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2287.83</v>
+        <v>1070.98</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1469-1545-CM26</t>
+          <t>1133353-37-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7915,17 +7915,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>7400.75</v>
+        <v>11721.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1133353-37-CM26</t>
+          <t>1469-1545-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7976,17 +7976,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>11721.5</v>
+        <v>7400.75</v>
       </c>
     </row>
     <row r="125">
@@ -8444,7 +8444,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2294-1037-CM26</t>
+          <t>2294-1036-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>4968.25</v>
+        <v>3893.56</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2294-1036-CM26</t>
+          <t>2294-1037-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3893.56</v>
+        <v>4968.25</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2294-1045-CM26</t>
+          <t>1233619-803-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8586,17 +8586,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>23011.55</v>
+        <v>2862.78</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1233619-803-CM26</t>
+          <t>2294-1045-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8647,17 +8647,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2862.78</v>
+        <v>23011.55</v>
       </c>
     </row>
     <row r="136">
@@ -8932,7 +8932,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4085-400-CM26</t>
+          <t>2298-512-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>IMunicipalidad de Molina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>8544.219999999999</v>
+        <v>4558.53</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2298-512-CM26</t>
+          <t>4085-400-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4558.53</v>
+        <v>8544.219999999999</v>
       </c>
     </row>
     <row r="142">
@@ -9176,7 +9176,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1469-1840-CM26</t>
+          <t>2445-2199-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9196,17 +9196,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>780.05</v>
+        <v>16898</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2445-2199-CM26</t>
+          <t>2445-2200-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>16898</v>
+        <v>2340.14</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2445-2200-CM26</t>
+          <t>1469-1840-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2340.14</v>
+        <v>780.05</v>
       </c>
     </row>
     <row r="147">
@@ -9664,7 +9664,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2294-1152-CM26</t>
+          <t>2294-1151-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2636.33</v>
+        <v>6592.48</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2294-1151-CM26</t>
+          <t>2294-1152-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>6592.48</v>
+        <v>2636.33</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4089-394-CM26</t>
+          <t>1391-1367-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.130.602-k</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>3237.23</v>
+        <v>541.21</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1391-1367-CM26</t>
+          <t>4089-394-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.130.602-k</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>541.21</v>
+        <v>3237.23</v>
       </c>
     </row>
     <row r="156">
@@ -10274,7 +10274,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2294-1411-CM26</t>
+          <t>2294-1127-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3956.75</v>
+        <v>2384.72</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2294-1127-CM26</t>
+          <t>2294-1411-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2384.72</v>
+        <v>3956.75</v>
       </c>
     </row>
     <row r="164">
@@ -10452,6 +10452,128 @@
       </c>
       <c r="M164" s="2" t="n">
         <v>6033.44</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>4404-180-CM26</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>18795.22</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>3251-516-CM26</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>69.252.700-3</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>3647</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/maule.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/maule.xlsx
@@ -562,7 +562,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1724,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1789,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1854,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1919,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1984,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2305,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2370,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2435,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2500,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2565,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2630,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2695,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2760,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2947,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3012,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3077,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3142,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3272,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3337,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3402,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3467,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3593,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3658,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3723,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3788,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3853,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3918,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3983,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4048,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4174,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4300,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4365,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4430,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4495,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4560,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4625,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4751,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4816,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4881,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +5007,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5072,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5137,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5202,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5267,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5332,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5397,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5462,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5527,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5653,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5718,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5783,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5909,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6035,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6100,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6226,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6291,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6356,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6482,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6547,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6612,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6677,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6742,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6807,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6872,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6937,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +7002,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7067,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7132,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7197,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7262,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7388,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7453,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7701,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7888,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7953,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8018,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8083,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8148,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8274,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8339,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8465,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8530,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8595,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8660,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8725,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8790,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8916,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8981,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9046,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8866,7 +9298,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9110,7 +9546,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9611,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9293,7 +9737,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9354,7 +9802,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9415,7 +9867,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9476,7 +9932,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9537,7 +9997,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9598,7 +10062,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9781,7 +10249,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9842,7 +10314,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9903,7 +10379,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10086,7 +10566,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10208,7 +10692,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10269,7 +10757,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10330,7 +10822,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10391,7 +10887,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10452,7 +10952,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10513,7 +11017,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10574,7 +11082,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10696,7 +11208,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10757,7 +11273,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10818,7 +11338,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10879,7 +11403,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10940,7 +11468,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11062,7 +11594,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11123,7 +11659,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11184,7 +11724,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11245,7 +11789,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11306,7 +11854,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11367,7 +11919,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11428,7 +11984,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11489,7 +12049,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11611,7 +12175,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11672,7 +12240,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11733,7 +12305,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11794,7 +12370,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11855,7 +12435,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11977,7 +12561,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12038,7 +12626,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12099,7 +12691,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12160,7 +12756,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12221,7 +12821,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12282,7 +12886,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12404,7 +13012,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12465,7 +13077,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12526,7 +13142,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12648,7 +13268,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12770,7 +13394,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12831,7 +13459,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12892,7 +13524,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12953,7 +13589,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13014,7 +13654,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13075,7 +13719,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13136,7 +13784,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13197,7 +13849,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13258,7 +13914,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13319,7 +13979,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13380,7 +14044,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13441,7 +14109,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13502,7 +14174,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13563,7 +14239,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13868,7 +14548,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13929,7 +14613,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13990,7 +14678,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14173,7 +14865,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14295,7 +14991,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14661,7 +15361,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14722,7 +15426,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14783,7 +15491,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14844,7 +15556,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14966,7 +15682,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15027,7 +15747,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15149,7 +15873,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15210,7 +15938,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15271,7 +16003,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15393,7 +16129,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15454,7 +16194,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15515,7 +16259,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15576,7 +16324,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15698,7 +16450,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15759,7 +16515,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16003,7 +16763,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16064,7 +16828,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16125,7 +16893,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16308,7 +17080,11 @@
           <t>77.319.537-4</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16369,7 +17145,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16491,7 +17271,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16552,7 +17336,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16613,7 +17401,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16674,7 +17466,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16735,7 +17531,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16796,7 +17596,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16857,7 +17661,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16918,7 +17726,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16979,7 +17791,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17040,7 +17856,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17101,7 +17921,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17162,7 +17986,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17223,7 +18051,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +18177,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +18242,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17528,7 +18368,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18433,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17833,7 +18681,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17894,7 +18746,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17955,7 +18811,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18016,7 +18876,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18077,7 +18941,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18138,7 +19006,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18260,7 +19132,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18321,7 +19197,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18504,7 +19384,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18809,7 +19693,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18870,7 +19758,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18931,7 +19823,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18992,7 +19888,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19053,7 +19953,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19114,7 +20018,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19175,7 +20083,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19297,7 +20209,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19358,7 +20274,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19419,7 +20339,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19541,7 +20465,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19602,7 +20530,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19663,7 +20595,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19724,7 +20660,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19785,7 +20725,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19907,7 +20851,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20029,7 +20977,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20151,7 +21103,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20212,7 +21168,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20273,7 +21233,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20334,7 +21298,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20395,7 +21363,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20456,7 +21428,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20517,7 +21493,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20578,7 +21558,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20639,7 +21623,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20826,7 +21814,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20887,7 +21879,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21009,7 +22005,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21131,7 +22131,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21253,7 +22257,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21314,7 +22322,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21375,7 +22387,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21436,7 +22452,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21558,7 +22578,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21619,7 +22643,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21680,7 +22708,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21741,7 +22773,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21802,7 +22838,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21863,7 +22903,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21924,7 +22968,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21985,7 +23033,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22046,7 +23098,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22168,7 +23224,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/maule.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M356"/>
+  <dimension ref="A1:M369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1229,7 +1229,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2309-53-CM25</t>
+          <t>2311-2658-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1269,32 +1269,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7435.12</v>
+        <v>8333.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2311-2658-CM25</t>
+          <t>2309-53-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1314,7 +1310,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1334,22 +1330,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8333.67</v>
+        <v>7435.12</v>
       </c>
     </row>
     <row r="15">
@@ -1420,7 +1420,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1233619-128-CM25</t>
+          <t>1233619-126-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>20808.34</v>
+        <v>9263.559999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1550,7 +1550,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1233619-126-CM25</t>
+          <t>1233619-128-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>9263.559999999999</v>
+        <v>20808.34</v>
       </c>
     </row>
     <row r="19">
@@ -1676,7 +1676,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4690-84-CM25</t>
+          <t>840405-7-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.110.700-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2748.9</v>
+        <v>7376</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>840405-7-CM25</t>
+          <t>4690-84-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.110.700-0</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7376</v>
+        <v>2748.9</v>
       </c>
     </row>
     <row r="22">
@@ -2062,7 +2062,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3251-158-CM25</t>
+          <t>3968-51-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2082,17 +2082,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.100.600-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE HUALANE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2553.62</v>
+        <v>8641.879999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3968-51-CM25</t>
+          <t>3251-158-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2147,17 +2147,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.100.600-K</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALANE</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8641.879999999999</v>
+        <v>2553.62</v>
       </c>
     </row>
     <row r="28">
@@ -2257,7 +2257,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4401-204-CM25</t>
+          <t>3024-229-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.130.800-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2316,13 +2316,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>20946.07</v>
+        <v>16197.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3024-229-CM25</t>
+          <t>4401-204-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>16197.09</v>
+        <v>20946.07</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3696-86-CM25</t>
+          <t>1469-432-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15949.25</v>
+        <v>18171.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1469-432-CM25</t>
+          <t>3696-86-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2492,12 +2492,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>18171.3</v>
+        <v>15949.25</v>
       </c>
     </row>
     <row r="33">
@@ -4000,7 +4000,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2294-749-CM25</t>
+          <t>2294-740-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4040,32 +4040,28 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIAL FELP SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.427.199-8</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>6344.78</v>
+        <v>4462.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2294-740-CM25</t>
+          <t>2294-749-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4105,22 +4101,26 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COMERCIAL FELP SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.427.199-8</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4462.5</v>
+        <v>6344.78</v>
       </c>
     </row>
     <row r="58">
@@ -4191,7 +4191,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2294-784-CM25</t>
+          <t>4159-292-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4231,28 +4231,32 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5401.17</v>
+        <v>21082.79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2294-777-CM25</t>
+          <t>552578-48-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4277,12 +4281,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4292,17 +4296,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4311,13 +4315,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2208.54</v>
+        <v>23333.52</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>552578-48-CM25</t>
+          <t>2294-777-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4342,12 +4346,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4357,17 +4361,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4376,13 +4380,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>23333.52</v>
+        <v>2208.54</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4159-292-CM25</t>
+          <t>2294-784-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4402,17 +4406,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4422,32 +4426,28 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>21082.79</v>
+        <v>5401.17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2294-804-CM25</t>
+          <t>2294-797-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4506,13 +4506,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2537.79</v>
+        <v>3114.17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2294-797-CM25</t>
+          <t>2294-804-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4571,13 +4571,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3114.17</v>
+        <v>2537.79</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2294-927-CM25</t>
+          <t>2294-907-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4617,17 +4617,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>12688.97</v>
+        <v>8329.76</v>
       </c>
     </row>
     <row r="66">
@@ -4703,7 +4703,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2294-907-CM25</t>
+          <t>2294-927-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8329.76</v>
+        <v>12688.97</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2294-938-CM25</t>
+          <t>3024-593-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4788,17 +4788,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.800-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3312.89</v>
+        <v>6223.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2294-946-CM25</t>
+          <t>2294-935-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4873,32 +4873,28 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>23055.95</v>
+        <v>7833.77</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2294-935-CM25</t>
+          <t>2294-938-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4938,28 +4934,32 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7833.77</v>
+        <v>3312.89</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3024-593-CM25</t>
+          <t>2294-940-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4979,17 +4979,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6223.7</v>
+        <v>9965.35</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2294-940-CM25</t>
+          <t>2294-946-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9965.35</v>
+        <v>23055.95</v>
       </c>
     </row>
     <row r="73">
@@ -5349,7 +5349,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1233619-442-CM25</t>
+          <t>2294-1121-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5369,17 +5369,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5389,32 +5389,28 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>8578.92</v>
+        <v>12398</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2292-725-CM25</t>
+          <t>2294-1123-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5454,17 +5450,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5473,13 +5469,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>35735.7</v>
+        <v>17255</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2294-1123-CM25</t>
+          <t>1233619-442-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5499,17 +5495,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5519,17 +5515,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5538,13 +5534,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>17255</v>
+        <v>8578.92</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2294-1121-CM25</t>
+          <t>2292-725-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5584,28 +5580,32 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>12398</v>
+        <v>35735.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3843-118-CM25</t>
+          <t>1469-1558-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5664,13 +5664,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>6611.64</v>
+        <v>46765.93</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1469-1558-CM25</t>
+          <t>3843-118-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5695,12 +5695,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>46765.93</v>
+        <v>6611.64</v>
       </c>
     </row>
     <row r="83">
@@ -5861,7 +5861,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4171-479-CM25</t>
+          <t>2294-1269-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.834.500-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5920,13 +5920,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>13588.38</v>
+        <v>2946.44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2294-1247-CM25</t>
+          <t>4171-479-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.834.500-8</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5966,28 +5966,32 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3675.26</v>
+        <v>13588.38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2294-1269-CM25</t>
+          <t>2294-1247-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6027,26 +6031,22 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2946.44</v>
+        <v>3675.26</v>
       </c>
     </row>
     <row r="88">
@@ -6308,7 +6308,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2294-848-CM25</t>
+          <t>3766-151-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6328,17 +6328,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6348,32 +6348,28 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>40493.92</v>
+        <v>7531.99</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3766-151-CM25</t>
+          <t>2294-848-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6393,17 +6389,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6413,28 +6409,32 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7531.99</v>
+        <v>40493.92</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4689-279-CM25</t>
+          <t>4089-410-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6454,17 +6454,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.130.602-k</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6493,13 +6493,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5901.9</v>
+        <v>8063.44</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4089-410-CM25</t>
+          <t>4689-279-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.130.602-k</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6539,12 +6539,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8063.44</v>
+        <v>5901.9</v>
       </c>
     </row>
     <row r="96">
@@ -7149,7 +7149,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2445-3216-CM25</t>
+          <t>2445-3214-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -7208,13 +7208,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>15214.27</v>
+        <v>8770.780000000001</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2445-3214-CM25</t>
+          <t>2445-3216-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>8770.780000000001</v>
+        <v>15214.27</v>
       </c>
     </row>
     <row r="107">
@@ -7592,7 +7592,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2294-1743-CM25</t>
+          <t>872535-255-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7612,17 +7612,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7632,28 +7632,32 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>10834.95</v>
+        <v>6372.45</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>872535-255-CM25</t>
+          <t>2292-1087-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7673,17 +7677,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7693,32 +7697,28 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6372.45</v>
+        <v>2593.72</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4315-301-CM25</t>
+          <t>2825-375-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7738,17 +7738,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curepto</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7758,28 +7758,32 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>4337.48</v>
+        <v>6079.71</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2292-1087-CM25</t>
+          <t>4315-301-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7799,17 +7803,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7819,12 +7823,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7834,13 +7838,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2593.72</v>
+        <v>4337.48</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2825-375-CM25</t>
+          <t>2294-1742-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7865,12 +7869,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7880,12 +7884,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7899,13 +7903,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>6079.71</v>
+        <v>27227.2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2294-1742-CM25</t>
+          <t>2294-1743-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7945,26 +7949,22 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>27227.2</v>
+        <v>10834.95</v>
       </c>
     </row>
     <row r="118">
@@ -8100,7 +8100,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1469-2416-CM25</t>
+          <t>2294-1944-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8140,32 +8140,28 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2237.08</v>
+        <v>11887.15</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2294-1944-CM25</t>
+          <t>1469-2416-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8190,12 +8186,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8205,22 +8201,26 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>11887.15</v>
+        <v>2237.08</v>
       </c>
     </row>
     <row r="122">
@@ -9124,7 +9124,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2292-1314-CM25</t>
+          <t>2825-478-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9164,22 +9164,26 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>34981.94</v>
+        <v>2779.07</v>
       </c>
     </row>
     <row r="137">
@@ -9250,7 +9254,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2825-478-CM25</t>
+          <t>2292-1314-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9275,12 +9279,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9290,26 +9294,22 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2779.07</v>
+        <v>34981.94</v>
       </c>
     </row>
     <row r="139">
@@ -9498,7 +9498,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1719-194-CM25</t>
+          <t>2311-3253-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9557,13 +9557,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2932.16</v>
+        <v>2320.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2311-3253-CM25</t>
+          <t>1719-194-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2320.5</v>
+        <v>2932.16</v>
       </c>
     </row>
     <row r="144">
@@ -9884,7 +9884,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2292-9171-CM25</t>
+          <t>2436-1286-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9904,17 +9904,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9924,12 +9924,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9943,13 +9943,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>10414.62</v>
+        <v>4292.93</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2436-1286-CM25</t>
+          <t>2292-9171-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9969,17 +9969,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>4292.93</v>
+        <v>10414.62</v>
       </c>
     </row>
     <row r="150">
@@ -10396,7 +10396,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4605-220-CM25</t>
+          <t>1069417-2581-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.819.000-5</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.292.976-7</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>21485.18</v>
+        <v>7943.25</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1069417-2581-CM25</t>
+          <t>4605-220-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>61.819.000-5</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>7943.25</v>
+        <v>21485.18</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1133353-36-CM25</t>
+          <t>3766-300-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10538,17 +10538,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10558,32 +10558,28 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>12921.62</v>
+        <v>4283.94</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3766-300-CM25</t>
+          <t>1133353-36-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10603,17 +10599,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10623,28 +10619,32 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4283.94</v>
+        <v>12921.62</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2440-1947-CM25</t>
+          <t>3251-1841-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10664,17 +10664,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -10703,13 +10703,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>30154.18</v>
+        <v>7752.97</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3251-1841-CM25</t>
+          <t>2440-1947-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10729,17 +10729,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -10768,13 +10768,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>7752.97</v>
+        <v>30154.18</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2440-2026-CM25</t>
+          <t>1233619-1413-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10794,17 +10794,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -10833,13 +10833,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>17284.45</v>
+        <v>8231.879999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1233619-1413-CM25</t>
+          <t>2440-2026-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10859,17 +10859,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -10898,7 +10898,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8231.879999999999</v>
+        <v>17284.45</v>
       </c>
     </row>
     <row r="164">
@@ -11099,7 +11099,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4404-811-CM25</t>
+          <t>4404-810-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11139,28 +11139,32 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>36727.68</v>
+        <v>35879.64</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4404-810-CM25</t>
+          <t>4404-811-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11200,26 +11204,22 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>77.152.668-3</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>35879.64</v>
+        <v>36727.68</v>
       </c>
     </row>
     <row r="169">
@@ -12838,7 +12838,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1456838-12-CM26</t>
+          <t>1456838-13-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12878,32 +12878,28 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>57695.27</v>
+        <v>3058.06</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1456838-13-CM26</t>
+          <t>1456838-12-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12943,22 +12939,26 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3058.06</v>
+        <v>57695.27</v>
       </c>
     </row>
     <row r="196">
@@ -13220,7 +13220,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3470-14-CM26</t>
+          <t>1079566-95-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13245,12 +13245,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13260,32 +13260,28 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>7119.04</v>
+        <v>4730.25</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1079566-95-CM26</t>
+          <t>3470-14-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13310,12 +13306,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13325,22 +13321,26 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>4730.25</v>
+        <v>7119.04</v>
       </c>
     </row>
     <row r="202">
@@ -13411,7 +13411,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2440-199-CM26</t>
+          <t>636811-54-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13431,17 +13431,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13451,12 +13451,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -13470,13 +13470,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>6675.9</v>
+        <v>16228.68</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>636811-54-CM26</t>
+          <t>2440-198-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13496,17 +13496,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13516,17 +13516,17 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13535,13 +13535,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>16228.68</v>
+        <v>3031.11</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2440-198-CM26</t>
+          <t>2440-199-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13581,17 +13581,17 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13600,7 +13600,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3031.11</v>
+        <v>6675.9</v>
       </c>
     </row>
     <row r="206">
@@ -13671,7 +13671,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2298-214-CM26</t>
+          <t>2291-412-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13691,17 +13691,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -13730,13 +13730,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2373.01</v>
+        <v>3351.64</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2505-53-CM26</t>
+          <t>4085-177-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13761,12 +13761,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.110.700-0</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO CLARO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>COBROTECH SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.819.088-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -13795,13 +13795,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5347.86</v>
+        <v>10648.43</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4085-181-CM26</t>
+          <t>4085-178-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>SYSCAM TECHNOLOGIES SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.137.827-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -13860,13 +13860,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>4112.37</v>
+        <v>956.15</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2291-412-CM26</t>
+          <t>4085-181-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13886,17 +13886,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13906,12 +13906,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -13925,13 +13925,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3351.64</v>
+        <v>4112.37</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>4085-177-CM26</t>
+          <t>2505-53-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13956,12 +13956,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.110.700-0</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE RIO CLARO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13971,12 +13971,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COBROTECH SPA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.819.088-7</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -13990,13 +13990,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>10648.43</v>
+        <v>5347.86</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>4085-178-CM26</t>
+          <t>2298-214-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14021,12 +14021,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14036,12 +14036,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14055,7 +14055,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>956.15</v>
+        <v>2373.01</v>
       </c>
     </row>
     <row r="213">
@@ -14630,7 +14630,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2318-260-CM26</t>
+          <t>1233619-458-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14655,12 +14655,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14670,32 +14670,28 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>12111.7</v>
+        <v>5540.64</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1233619-458-CM26</t>
+          <t>2318-260-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14720,12 +14716,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14735,22 +14731,26 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr"/>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>5540.64</v>
+        <v>12111.7</v>
       </c>
     </row>
     <row r="224">
@@ -15008,7 +15008,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1233619-513-CM26</t>
+          <t>1233619-514-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15069,7 +15069,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1233619-514-CM26</t>
+          <t>1233619-513-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15130,7 +15130,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1233619-511-CM26</t>
+          <t>1233619-512-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15191,7 +15191,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1233619-510-CM26</t>
+          <t>1233619-511-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>6193.69</v>
+        <v>11566.66</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1233619-512-CM26</t>
+          <t>1233619-510-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>11566.66</v>
+        <v>6193.69</v>
       </c>
     </row>
     <row r="233">
@@ -15764,7 +15764,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2827-353-CM26</t>
+          <t>2827-354-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15804,28 +15804,32 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>24676.6</v>
+        <v>1649.34</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2440-469-CM26</t>
+          <t>2827-353-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15845,17 +15849,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15865,32 +15869,28 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>5386.23</v>
+        <v>24676.6</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2827-354-CM26</t>
+          <t>2440-469-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15910,17 +15910,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15930,17 +15930,17 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -15949,13 +15949,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1649.34</v>
+        <v>5386.23</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2294-483-CM26</t>
+          <t>2294-467-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15995,12 +15995,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -16014,13 +16014,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2132.48</v>
+        <v>2072.74</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2294-476-CM26</t>
+          <t>2294-445-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16060,28 +16060,32 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>30421.73</v>
+        <v>10448.2</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2294-445-CM26</t>
+          <t>2294-421-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16121,32 +16125,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>10448.2</v>
+        <v>1606.45</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2294-467-CM26</t>
+          <t>2294-420-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16186,12 +16186,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -16205,13 +16205,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2072.74</v>
+        <v>32643.37</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2294-420-CM26</t>
+          <t>2294-419-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -16270,13 +16270,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>32643.37</v>
+        <v>10363.71</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2294-419-CM26</t>
+          <t>2294-476-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16316,32 +16316,28 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.968.900-6</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>10363.71</v>
+        <v>30421.73</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2294-421-CM26</t>
+          <t>2294-483-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16381,28 +16377,32 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1606.45</v>
+        <v>2132.48</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2294-471-CM26</t>
+          <t>3807-199-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16427,12 +16427,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.120.200-3</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16442,12 +16442,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -16461,13 +16461,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>6632.77</v>
+        <v>755.64</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3807-199-CM26</t>
+          <t>2294-471-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16492,12 +16492,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16507,12 +16507,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -16526,7 +16526,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>755.64</v>
+        <v>6632.77</v>
       </c>
     </row>
     <row r="252">
@@ -16654,7 +16654,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2294-542-CM26</t>
+          <t>1233619-623-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16674,17 +16674,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16694,12 +16694,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -16709,13 +16709,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1570.51</v>
+        <v>20122.66</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2294-543-CM26</t>
+          <t>1469-1300-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16755,12 +16755,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -16774,7 +16774,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>195.99</v>
+        <v>11405.56</v>
       </c>
     </row>
     <row r="256">
@@ -16845,7 +16845,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1469-1300-CM26</t>
+          <t>2294-543-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16885,12 +16885,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -16904,13 +16904,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>11405.56</v>
+        <v>195.99</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1233619-623-CM26</t>
+          <t>2294-542-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16930,17 +16930,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16950,12 +16950,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>20122.66</v>
+        <v>1570.51</v>
       </c>
     </row>
     <row r="259">
@@ -17097,7 +17097,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2294-655-CM26</t>
+          <t>4690-163-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17122,12 +17122,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17137,12 +17137,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -17156,13 +17156,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>9460.5</v>
+        <v>5097.53</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1233619-665-CM26</t>
+          <t>4690-161-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17182,17 +17182,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17202,28 +17202,32 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3849.33</v>
+        <v>1209.02</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>4690-161-CM26</t>
+          <t>1233619-665-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17243,17 +17247,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17263,32 +17267,28 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1209.02</v>
+        <v>3849.33</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>4690-162-CM26</t>
+          <t>2294-655-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17313,12 +17313,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -17328,12 +17328,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -17347,13 +17347,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>8495.889999999999</v>
+        <v>9460.5</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4690-163-CM26</t>
+          <t>4690-162-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17412,13 +17412,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>5097.53</v>
+        <v>8495.889999999999</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2294-642-CM26</t>
+          <t>2318-411-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17438,17 +17438,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17458,12 +17458,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -17477,7 +17477,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>9608.66</v>
+        <v>1523.06</v>
       </c>
     </row>
     <row r="267">
@@ -17548,7 +17548,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2318-411-CM26</t>
+          <t>2294-642-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17568,17 +17568,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17588,12 +17588,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -17607,13 +17607,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1523.06</v>
+        <v>9608.66</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2294-720-CM26</t>
+          <t>2294-721-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17653,12 +17653,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -17672,13 +17672,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>7680.26</v>
+        <v>29658.67</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2294-721-CM26</t>
+          <t>2294-720-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -17737,13 +17737,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>29658.67</v>
+        <v>7680.26</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1233619-684-CM26</t>
+          <t>2291-912-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17768,12 +17768,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17783,12 +17783,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -17802,13 +17802,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2105.59</v>
+        <v>962.16</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2291-912-CM26</t>
+          <t>1233619-684-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -17867,7 +17867,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>962.16</v>
+        <v>2105.59</v>
       </c>
     </row>
     <row r="273">
@@ -17938,7 +17938,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1233619-690-CM26</t>
+          <t>2294-799-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17958,17 +17958,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17978,12 +17978,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -17997,13 +17997,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>103.41</v>
+        <v>2212.21</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2294-799-CM26</t>
+          <t>1233619-690-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18023,17 +18023,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18043,12 +18043,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -18062,7 +18062,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2212.21</v>
+        <v>103.41</v>
       </c>
     </row>
     <row r="276">
@@ -18129,7 +18129,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2298-411-CM26</t>
+          <t>2298-412-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18169,12 +18169,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -18188,13 +18188,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>12259.38</v>
+        <v>3071.84</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2298-412-CM26</t>
+          <t>2298-411-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18234,12 +18234,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>3071.84</v>
+        <v>12259.38</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1233619-742-CM26</t>
+          <t>2827-415-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18284,12 +18284,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18299,28 +18299,32 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2287.83</v>
+        <v>1070.98</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2827-415-CM26</t>
+          <t>1233619-742-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18345,12 +18349,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18360,26 +18364,22 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1070.98</v>
+        <v>2287.83</v>
       </c>
     </row>
     <row r="281">
@@ -18763,7 +18763,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2440-841-CM26</t>
+          <t>2294-797-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18788,12 +18788,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18803,17 +18803,17 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -18822,13 +18822,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>5051.49</v>
+        <v>84.48999999999999</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2294-1006-CM26</t>
+          <t>1389488-458-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18848,17 +18848,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.981.320-0</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18868,12 +18868,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -18887,13 +18887,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>11224.38</v>
+        <v>6068.88</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2294-797-CM26</t>
+          <t>2294-1006-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18933,12 +18933,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -18952,13 +18952,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>84.48999999999999</v>
+        <v>11224.38</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1389488-458-CM26</t>
+          <t>2440-841-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18978,17 +18978,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.981.320-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18998,17 +18998,17 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -19017,13 +19017,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>6068.88</v>
+        <v>5051.49</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2294-1036-CM26</t>
+          <t>2294-1037-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19063,28 +19063,32 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K291" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>3893.56</v>
+        <v>4968.25</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2294-1037-CM26</t>
+          <t>2294-1036-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19124,26 +19128,22 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>4968.25</v>
+        <v>3893.56</v>
       </c>
     </row>
     <row r="293">
@@ -19401,7 +19401,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1233619-814-CM26</t>
+          <t>1233619-824-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19441,12 +19441,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -19456,13 +19456,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>19085.22</v>
+        <v>10572.91</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1233619-824-CM26</t>
+          <t>1233619-814-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19502,12 +19502,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -19517,7 +19517,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>10572.91</v>
+        <v>19085.22</v>
       </c>
     </row>
     <row r="299">
@@ -19840,7 +19840,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1469-1840-CM26</t>
+          <t>2445-2199-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19860,17 +19860,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19880,12 +19880,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -19899,13 +19899,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>780.05</v>
+        <v>16898</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2445-2199-CM26</t>
+          <t>2445-2200-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19945,12 +19945,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -19964,13 +19964,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>16898</v>
+        <v>2340.14</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2445-2200-CM26</t>
+          <t>1469-1840-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19990,17 +19990,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20029,7 +20029,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>2340.14</v>
+        <v>780.05</v>
       </c>
     </row>
     <row r="307">
@@ -20100,7 +20100,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2595-246-CM26</t>
+          <t>1233619-882-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20125,12 +20125,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20140,22 +20140,26 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>3968.88</v>
+        <v>1281.42</v>
       </c>
     </row>
     <row r="309">
@@ -20226,7 +20230,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1233619-882-CM26</t>
+          <t>2595-246-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20251,12 +20255,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20266,26 +20270,22 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1281.42</v>
+        <v>3968.88</v>
       </c>
     </row>
     <row r="311">
@@ -20356,7 +20356,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2294-1151-CM26</t>
+          <t>2294-1152-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20396,28 +20396,32 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>6592.48</v>
+        <v>2636.33</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2294-1152-CM26</t>
+          <t>2294-1151-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20457,26 +20461,22 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2636.33</v>
+        <v>6592.48</v>
       </c>
     </row>
     <row r="314">
@@ -20742,7 +20742,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1233619-917-CM26</t>
+          <t>2294-1392-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20782,28 +20782,32 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>570.01</v>
+        <v>5783.16</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2294-1392-CM26</t>
+          <t>1233619-917-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20828,12 +20832,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -20843,26 +20847,22 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>5783.16</v>
+        <v>570.01</v>
       </c>
     </row>
     <row r="320">
@@ -20994,7 +20994,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2294-1127-CM26</t>
+          <t>2294-1411-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21034,28 +21034,32 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2384.72</v>
+        <v>3956.75</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2294-1411-CM26</t>
+          <t>2294-1127-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21095,32 +21099,28 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>3956.75</v>
+        <v>2384.72</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1499664-50-CM26</t>
+          <t>434-735-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21140,17 +21140,17 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>65.258.927-8</t>
+          <t>69.120.400-6</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>FUNDACIÓN GG</t>
+          <t>I MUNICIPALIDAD DE CAUQUENES</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21160,12 +21160,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -21179,13 +21179,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2431.66</v>
+        <v>15496.22</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>434-735-CM26</t>
+          <t>1499664-50-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21205,17 +21205,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>69.120.400-6</t>
+          <t>65.258.927-8</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CAUQUENES</t>
+          <t>FUNDACIÓN GG</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21225,12 +21225,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -21244,7 +21244,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>15496.22</v>
+        <v>2431.66</v>
       </c>
     </row>
     <row r="326">
@@ -21315,7 +21315,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2294-1469-CM26</t>
+          <t>3253-243-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21335,17 +21335,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21355,17 +21355,17 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -21374,13 +21374,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>33799.97</v>
+        <v>2934.54</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>3253-243-CM26</t>
+          <t>2294-1469-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21400,17 +21400,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21420,17 +21420,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2934.54</v>
+        <v>33799.97</v>
       </c>
     </row>
     <row r="329">
@@ -21510,7 +21510,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2595-314-CM26</t>
+          <t>3843-206-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21535,12 +21535,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21550,17 +21550,17 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -21569,13 +21569,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>3682.37</v>
+        <v>35643.24</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>3843-206-CM26</t>
+          <t>2595-314-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21600,12 +21600,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21615,17 +21615,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>35643.24</v>
+        <v>3682.37</v>
       </c>
     </row>
     <row r="332">
@@ -21705,7 +21705,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>3287-402-CM26</t>
+          <t>3251-516-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21730,12 +21730,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21745,22 +21745,26 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>76.596.570-5</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1005.54</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="334">
@@ -21831,7 +21835,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>3251-516-CM26</t>
+          <t>3287-402-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21856,12 +21860,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -21871,32 +21875,28 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3647</v>
+        <v>1005.54</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2294-1560-CM26</t>
+          <t>3299-300-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -21921,12 +21921,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21936,28 +21936,32 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K336" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>13579.99</v>
+        <v>4022.15</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>3299-300-CM26</t>
+          <t>2294-1560-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21982,12 +21986,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21997,32 +22001,28 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>4022.15</v>
+        <v>13579.99</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1469-2347-CM26</t>
+          <t>2292-6953-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22042,17 +22042,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22062,12 +22062,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K338" t="inlineStr"/>
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>15261.75</v>
+        <v>2719.03</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>3287-426-CM26</t>
+          <t>1469-2347-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22108,12 +22108,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -22123,32 +22123,28 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
-        </is>
-      </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>3016.61</v>
+        <v>15261.75</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2292-6953-CM26</t>
+          <t>3287-426-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22168,17 +22164,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22188,22 +22184,26 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K340" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2719.03</v>
+        <v>3016.61</v>
       </c>
     </row>
     <row r="341">
@@ -22274,7 +22274,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2320-300-CM26</t>
+          <t>3299-314-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22294,17 +22294,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22314,17 +22314,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -22333,7 +22333,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>5537.03</v>
+        <v>13072</v>
       </c>
     </row>
     <row r="343">
@@ -22404,7 +22404,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>3299-314-CM26</t>
+          <t>2320-300-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22424,17 +22424,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22444,17 +22444,17 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -22463,7 +22463,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>13072</v>
+        <v>5537.03</v>
       </c>
     </row>
     <row r="345">
@@ -22530,7 +22530,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2294-1812-CM26</t>
+          <t>2292-7075-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22570,17 +22570,17 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -22589,7 +22589,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>6069</v>
+        <v>19312.82</v>
       </c>
     </row>
     <row r="347">
@@ -22660,7 +22660,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2292-7075-CM26</t>
+          <t>2294-1812-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -22700,17 +22700,17 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -22719,7 +22719,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>19312.82</v>
+        <v>6069</v>
       </c>
     </row>
     <row r="349">
@@ -22745,7 +22745,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -22790,7 +22790,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2047-79-CM26</t>
+          <t>1467-56-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22815,12 +22815,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>60.511.073-8</t>
+          <t>60.511.071-1</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LINARES</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CURICÓ</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22855,7 +22855,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1142-266-CM26</t>
+          <t>1469-2718-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -22880,12 +22880,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>60.511.070-3</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -22895,12 +22895,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -22914,7 +22914,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>3152.31</v>
+        <v>22874.78</v>
       </c>
     </row>
     <row r="352">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -22985,7 +22985,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1469-2718-CM26</t>
+          <t>1142-266-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23010,12 +23010,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.511.070-3</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23025,12 +23025,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>RICOH</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>96.513.980-k</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -23044,13 +23044,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>22874.78</v>
+        <v>3152.31</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1467-56-CM26</t>
+          <t>2047-79-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23075,12 +23075,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>60.511.071-1</t>
+          <t>60.511.073-8</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CURICÓ</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LINARES</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -23135,7 +23135,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -23236,6 +23236,839 @@
       </c>
       <c r="M356" s="2" t="n">
         <v>1141.67</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>1978-1091-CM26</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>61.606.900-4</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="n">
+        <v>49106.06</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>1469-3003-CM26</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="n">
+        <v>4402.98</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2294-2176-CM26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="n">
+        <v>2827.82</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>3299-399-CM26</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>69.100.500-3</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>COMPUTACION INTEGRAL S A</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="n">
+        <v>6302.24</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>3206-352-CM26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>69.264.500-6</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="n">
+        <v>8844.32</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>1469-3072-CM26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="n">
+        <v>72503.13</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>1596-265-CM26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="n">
+        <v>2915.58</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>1596-267-CM26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>A &amp; S TECNOLOGIAS COMPUTACIONALES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>77.495.960-2</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="n">
+        <v>6723.5</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>1596-268-CM26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="n">
+        <v>20099.81</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>1469-3103-CM26</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="n">
+        <v>2974.88</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>1467-60-CM26</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>60.511.071-1</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CURICÓ</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="n">
+        <v>1386.9</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2294-2250-CM26</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="n">
+        <v>1499.4</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>4451-672-CM26</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="n">
+        <v>7363.72</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/maule.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/maule.xlsx
@@ -18783,7 +18783,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -20949,7 +20949,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -21400,7 +21400,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
